--- a/hr_toolkit/templates/insurance_ledger_template.xlsx
+++ b/hr_toolkit/templates/insurance_ledger_template.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9204"/>
+    <workbookView windowHeight="14800"/>
   </bookViews>
   <sheets>
     <sheet name="保险台账" sheetId="1" r:id="rId1"/>
@@ -32,74 +32,6 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>姓名</t>
-  </si>
-  <si>
-    <t>身份证号码</t>
-  </si>
-  <si>
-    <t>项目/部门</t>
-  </si>
-  <si>
-    <t>保单号1</t>
-  </si>
-  <si>
-    <t>保额</t>
-  </si>
-  <si>
-    <t>保单号2</t>
-  </si>
-  <si>
-    <t>保额合计</t>
-  </si>
-  <si>
-    <t>金三</t>
-  </si>
-  <si>
-    <t>330424123456241614</t>
-  </si>
-  <si>
-    <t>PZDX202536010000000011</t>
-  </si>
-  <si>
-    <t>PEAC202536010000000431</t>
-  </si>
-  <si>
-    <t>金四</t>
-  </si>
-  <si>
-    <t>413026123456095128</t>
-  </si>
-  <si>
-    <t>金五</t>
-  </si>
-  <si>
-    <t>320911123456171215</t>
-  </si>
-  <si>
-    <t>金六</t>
-  </si>
-  <si>
-    <t>411521123456155377</t>
-  </si>
-  <si>
-    <t>金七</t>
-  </si>
-  <si>
-    <t>362523123456066014</t>
-  </si>
-  <si>
-    <t>项目/部门：此列数据来源人员花名册中部门</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
@@ -455,27 +387,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -602,7 +519,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -614,34 +531,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -726,18 +643,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1283,184 +1194,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:I10"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88461538461539" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="2" width="8.88888888888889" style="1"/>
-    <col min="3" max="3" width="20.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7777777777778" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.4444444444444" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88888888888889" style="1"/>
-    <col min="7" max="7" width="25.4444444444444" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="2" width="8.88461538461539" style="1"/>
+    <col min="3" max="3" width="20.8846153846154" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7788461538462" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.4423076923077" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88461538461539" style="1"/>
+    <col min="7" max="7" width="25.4423076923077" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88461538461539" style="1"/>
   </cols>
-  <sheetData>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2">
-        <v>60</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="2">
-        <v>60</v>
-      </c>
-      <c r="I3" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
-        <v>60</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="2">
-        <v>60</v>
-      </c>
-      <c r="I4" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2">
-        <v>60</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="2">
-        <v>60</v>
-      </c>
-      <c r="I5" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2">
-        <v>60</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="2">
-        <v>60</v>
-      </c>
-      <c r="I6" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2">
-        <v>60</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
